--- a/week4/ticket_data.xlsx
+++ b/week4/ticket_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="292">
   <si>
     <t>Ticket IDs Sequence</t>
   </si>
@@ -304,126 +304,6 @@
     <t>02313</t>
   </si>
   <si>
-    <t>01972</t>
-  </si>
-  <si>
-    <t>01971</t>
-  </si>
-  <si>
-    <t>01970</t>
-  </si>
-  <si>
-    <t>01969</t>
-  </si>
-  <si>
-    <t>01968</t>
-  </si>
-  <si>
-    <t>01967</t>
-  </si>
-  <si>
-    <t>01966</t>
-  </si>
-  <si>
-    <t>01965</t>
-  </si>
-  <si>
-    <t>01964</t>
-  </si>
-  <si>
-    <t>01963</t>
-  </si>
-  <si>
-    <t>01962</t>
-  </si>
-  <si>
-    <t>01961</t>
-  </si>
-  <si>
-    <t>01960</t>
-  </si>
-  <si>
-    <t>01959</t>
-  </si>
-  <si>
-    <t>01958</t>
-  </si>
-  <si>
-    <t>01957</t>
-  </si>
-  <si>
-    <t>01956</t>
-  </si>
-  <si>
-    <t>01955</t>
-  </si>
-  <si>
-    <t>01954</t>
-  </si>
-  <si>
-    <t>01953</t>
-  </si>
-  <si>
-    <t>01952</t>
-  </si>
-  <si>
-    <t>01951</t>
-  </si>
-  <si>
-    <t>01950</t>
-  </si>
-  <si>
-    <t>01949</t>
-  </si>
-  <si>
-    <t>01948</t>
-  </si>
-  <si>
-    <t>01947</t>
-  </si>
-  <si>
-    <t>01946</t>
-  </si>
-  <si>
-    <t>01945</t>
-  </si>
-  <si>
-    <t>01944</t>
-  </si>
-  <si>
-    <t>01943</t>
-  </si>
-  <si>
-    <t>01942</t>
-  </si>
-  <si>
-    <t>01938</t>
-  </si>
-  <si>
-    <t>01937</t>
-  </si>
-  <si>
-    <t>01926</t>
-  </si>
-  <si>
-    <t>01925</t>
-  </si>
-  <si>
-    <t>01924</t>
-  </si>
-  <si>
-    <t>01923</t>
-  </si>
-  <si>
-    <t>01922</t>
-  </si>
-  <si>
-    <t>01921</t>
-  </si>
-  <si>
-    <t>01920</t>
-  </si>
-  <si>
     <t>02856</t>
   </si>
   <si>
@@ -697,138 +577,24 @@
     <t>MINDX ĐÀ NẴNG - HỖ TRỢ KIỂM TRA ĐỐI CHIẾU SỐ LƯỢNG ĐỔI QUÀ TRÊN DENISE</t>
   </si>
   <si>
-    <t>02002</t>
-  </si>
-  <si>
-    <t>02001</t>
-  </si>
-  <si>
-    <t>02000</t>
-  </si>
-  <si>
-    <t>01999</t>
-  </si>
-  <si>
-    <t>01998</t>
-  </si>
-  <si>
-    <t>01997</t>
-  </si>
-  <si>
-    <t>01996</t>
-  </si>
-  <si>
-    <t>01995</t>
-  </si>
-  <si>
-    <t>01994</t>
-  </si>
-  <si>
-    <t>01993</t>
-  </si>
-  <si>
-    <t>01992</t>
-  </si>
-  <si>
-    <t>01991</t>
-  </si>
-  <si>
-    <t>01990</t>
-  </si>
-  <si>
-    <t>01989</t>
-  </si>
-  <si>
-    <t>01988</t>
-  </si>
-  <si>
-    <t>01987</t>
-  </si>
-  <si>
-    <t>01986</t>
-  </si>
-  <si>
-    <t>01985</t>
-  </si>
-  <si>
-    <t>01984</t>
-  </si>
-  <si>
-    <t>01983</t>
-  </si>
-  <si>
-    <t>01982</t>
-  </si>
-  <si>
-    <t>01981</t>
-  </si>
-  <si>
-    <t>01980</t>
-  </si>
-  <si>
-    <t>01979</t>
-  </si>
-  <si>
-    <t>01978</t>
-  </si>
-  <si>
-    <t>01977</t>
-  </si>
-  <si>
-    <t>01976</t>
-  </si>
-  <si>
-    <t>01975</t>
-  </si>
-  <si>
-    <t>01974</t>
-  </si>
-  <si>
-    <t>01973</t>
-  </si>
-  <si>
-    <t>01939</t>
-  </si>
-  <si>
-    <t>01935</t>
-  </si>
-  <si>
-    <t>01934</t>
-  </si>
-  <si>
-    <t>01933</t>
-  </si>
-  <si>
-    <t>01932</t>
-  </si>
-  <si>
-    <t>01931</t>
-  </si>
-  <si>
-    <t>01930</t>
-  </si>
-  <si>
-    <t>01929</t>
-  </si>
-  <si>
-    <t>01928</t>
-  </si>
-  <si>
-    <t>01927</t>
-  </si>
-  <si>
-    <t>01915</t>
-  </si>
-  <si>
-    <t>01914</t>
+    <t>02963</t>
+  </si>
+  <si>
+    <t>Medium priority</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>02962</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
   <si>
     <t>02426</t>
   </si>
   <si>
-    <t>Medium priority</t>
-  </si>
-  <si>
     <t>Tech test</t>
   </si>
   <si>
@@ -880,33 +646,6 @@
     <t>Trạng thái lead</t>
   </si>
   <si>
-    <t>02033</t>
-  </si>
-  <si>
-    <t>02010</t>
-  </si>
-  <si>
-    <t>02009</t>
-  </si>
-  <si>
-    <t>02008</t>
-  </si>
-  <si>
-    <t>02007</t>
-  </si>
-  <si>
-    <t>02006</t>
-  </si>
-  <si>
-    <t>02005</t>
-  </si>
-  <si>
-    <t>02004</t>
-  </si>
-  <si>
-    <t>02003</t>
-  </si>
-  <si>
     <t>02858</t>
   </si>
   <si>
@@ -1151,126 +890,6 @@
   </si>
   <si>
     <t>02309</t>
-  </si>
-  <si>
-    <t>02044</t>
-  </si>
-  <si>
-    <t>02043</t>
-  </si>
-  <si>
-    <t>02042</t>
-  </si>
-  <si>
-    <t>02041</t>
-  </si>
-  <si>
-    <t>02040</t>
-  </si>
-  <si>
-    <t>02039</t>
-  </si>
-  <si>
-    <t>02038</t>
-  </si>
-  <si>
-    <t>02037</t>
-  </si>
-  <si>
-    <t>02036</t>
-  </si>
-  <si>
-    <t>02035</t>
-  </si>
-  <si>
-    <t>02034</t>
-  </si>
-  <si>
-    <t>02032</t>
-  </si>
-  <si>
-    <t>02031</t>
-  </si>
-  <si>
-    <t>02030</t>
-  </si>
-  <si>
-    <t>02029</t>
-  </si>
-  <si>
-    <t>02028</t>
-  </si>
-  <si>
-    <t>02027</t>
-  </si>
-  <si>
-    <t>02026</t>
-  </si>
-  <si>
-    <t>02025</t>
-  </si>
-  <si>
-    <t>02024</t>
-  </si>
-  <si>
-    <t>02023</t>
-  </si>
-  <si>
-    <t>02022</t>
-  </si>
-  <si>
-    <t>02021</t>
-  </si>
-  <si>
-    <t>02020</t>
-  </si>
-  <si>
-    <t>02019</t>
-  </si>
-  <si>
-    <t>02018</t>
-  </si>
-  <si>
-    <t>02017</t>
-  </si>
-  <si>
-    <t>02016</t>
-  </si>
-  <si>
-    <t>02015</t>
-  </si>
-  <si>
-    <t>02014</t>
-  </si>
-  <si>
-    <t>02013</t>
-  </si>
-  <si>
-    <t>02012</t>
-  </si>
-  <si>
-    <t>02011</t>
-  </si>
-  <si>
-    <t>01941</t>
-  </si>
-  <si>
-    <t>01940</t>
-  </si>
-  <si>
-    <t>01936</t>
-  </si>
-  <si>
-    <t>01919</t>
-  </si>
-  <si>
-    <t>01918</t>
-  </si>
-  <si>
-    <t>01917</t>
-  </si>
-  <si>
-    <t>01916</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I284"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="30.7109375" customWidth="1"/>
@@ -2620,10 +2239,10 @@
         <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2633,18 +2252,18 @@
         <v>12</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -2654,18 +2273,18 @@
         <v>12</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -2675,18 +2294,18 @@
         <v>12</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2696,18 +2315,18 @@
         <v>12</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -2717,18 +2336,18 @@
         <v>12</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -2738,18 +2357,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2759,18 +2378,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -2780,18 +2399,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -2806,13 +2425,13 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2827,13 +2446,13 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -2848,13 +2467,13 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -2869,13 +2488,13 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2890,13 +2509,13 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2911,13 +2530,13 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2932,13 +2551,13 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -2953,13 +2572,13 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -2974,13 +2593,13 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -2995,13 +2614,13 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -3016,13 +2635,13 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -3037,13 +2656,13 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -3058,13 +2677,13 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -3079,13 +2698,13 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -3100,13 +2719,13 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -3121,13 +2740,13 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -3142,13 +2761,13 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="2" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -3163,13 +2782,13 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="2" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -3184,13 +2803,13 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="2" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -3205,13 +2824,13 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -3226,13 +2845,13 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="2" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -3247,13 +2866,13 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -3268,13 +2887,13 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="2" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -3289,13 +2908,13 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="2" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -3310,13 +2929,13 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="2" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -3331,13 +2950,13 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="2" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -3352,13 +2971,13 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="2" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -3373,13 +2992,13 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="2" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -3394,13 +3013,13 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="2" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
@@ -3415,13 +3034,13 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="2" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
@@ -3436,13 +3055,13 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="2" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -3457,13 +3076,13 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="2" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
@@ -3473,18 +3092,18 @@
         <v>12</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="2" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -3494,18 +3113,18 @@
         <v>12</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="2" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -3515,18 +3134,18 @@
         <v>12</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -3536,18 +3155,18 @@
         <v>12</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="2" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
@@ -3557,18 +3176,18 @@
         <v>12</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="2" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
@@ -3578,18 +3197,18 @@
         <v>12</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="2" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
@@ -3599,18 +3218,18 @@
         <v>12</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
@@ -3620,18 +3239,18 @@
         <v>12</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -3646,13 +3265,13 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
@@ -3667,13 +3286,13 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="2" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
@@ -3688,13 +3307,13 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="2" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
@@ -3709,13 +3328,13 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="2" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
@@ -3730,13 +3349,13 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="2" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
@@ -3751,13 +3370,13 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="2" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
@@ -3772,13 +3391,13 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="2" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
@@ -3793,13 +3412,13 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="2" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
@@ -3814,13 +3433,13 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="2" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
@@ -3835,13 +3454,13 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="2" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
@@ -3856,13 +3475,13 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="2" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
@@ -3877,13 +3496,13 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="2" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -3898,13 +3517,13 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="2" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -3919,13 +3538,13 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="2" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -3935,18 +3554,18 @@
         <v>12</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="2" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
@@ -3956,18 +3575,18 @@
         <v>12</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
@@ -3977,20 +3596,22 @@
         <v>12</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="2" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D113" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -4003,13 +3624,13 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="2" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
@@ -4024,13 +3645,13 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="2" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
@@ -4045,13 +3666,13 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="2" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
@@ -4066,13 +3687,13 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="2" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
@@ -4087,13 +3708,13 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="2" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -4108,13 +3729,13 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="2" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -4129,13 +3750,13 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="2" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
@@ -4150,13 +3771,13 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="2" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
@@ -4171,13 +3792,13 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="2" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
@@ -4192,13 +3813,13 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="2" t="s">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -4213,13 +3834,13 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="2" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -4234,13 +3855,13 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="2" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
@@ -4255,13 +3876,13 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="2" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
@@ -4276,13 +3897,13 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="2" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>138</v>
+        <v>243</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
@@ -4297,13 +3918,13 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="2" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -4318,13 +3939,13 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="2" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -4339,13 +3960,13 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="2" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
@@ -4360,13 +3981,13 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="2" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
@@ -4381,13 +4002,13 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="2" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
@@ -4402,13 +4023,13 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="2" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
@@ -4423,13 +4044,13 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="2" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
@@ -4444,13 +4065,13 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="2" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
@@ -4465,13 +4086,13 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="2" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
@@ -4486,13 +4107,13 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="2" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>154</v>
+        <v>263</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
@@ -4507,13 +4128,13 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="2" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
@@ -4528,13 +4149,13 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="2" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>156</v>
+        <v>267</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
@@ -4549,13 +4170,13 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="2" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
@@ -4570,13 +4191,13 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="2" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
@@ -4591,13 +4212,13 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="2" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
@@ -4612,13 +4233,13 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="2" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
@@ -4633,13 +4254,13 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="2" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
@@ -4654,13 +4275,13 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="2" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>152</v>
+        <v>278</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
@@ -4675,13 +4296,13 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="2" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>168</v>
+        <v>280</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
@@ -4696,13 +4317,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="2" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
@@ -4717,13 +4338,13 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="2" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
@@ -4738,13 +4359,13 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="2" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
@@ -4759,13 +4380,13 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="2" t="s">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
@@ -4780,13 +4401,13 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="2" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
@@ -4801,13 +4422,13 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
@@ -4822,13 +4443,13 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="2" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>182</v>
+        <v>289</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
@@ -4843,13 +4464,13 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="2" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
@@ -4864,13 +4485,13 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="2" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
@@ -4883,2717 +4504,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
-      <c r="A156" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="A157" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9">
-      <c r="A158" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
-      <c r="A159" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9">
-      <c r="A160" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9">
-      <c r="A161" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I161" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9">
-      <c r="A162" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I162" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9">
-      <c r="A163" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-      <c r="H163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9">
-      <c r="A164" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9">
-      <c r="A165" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-      <c r="H165" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9">
-      <c r="A166" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-      <c r="H166" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I166" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9">
-      <c r="A167" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-      <c r="H167" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9">
-      <c r="A168" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-      <c r="H168" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I168" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9">
-      <c r="A169" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-      <c r="H169" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9">
-      <c r="A170" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-      <c r="H170" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9">
-      <c r="A171" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-      <c r="H171" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I171" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
-      <c r="A172" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-      <c r="H172" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I172" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9">
-      <c r="A173" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
-      <c r="A174" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9">
-      <c r="A175" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I175" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9">
-      <c r="A176" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I176" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
-      <c r="A177" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-      <c r="H177" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I177" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
-      <c r="A178" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-      <c r="H178" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
-      <c r="A179" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-      <c r="H179" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
-      <c r="A180" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-      <c r="H180" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
-      <c r="A181" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I181" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
-      <c r="A182" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I182" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9">
-      <c r="A183" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I183" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9">
-      <c r="A184" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I184" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
-      <c r="A185" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I185" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9">
-      <c r="A186" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I186" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9">
-      <c r="A187" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I187" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9">
-      <c r="A188" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I188" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9">
-      <c r="A189" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-      <c r="H189" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I189" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9">
-      <c r="A190" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-      <c r="H190" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9">
-      <c r="A191" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-      <c r="H191" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I191" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9">
-      <c r="A192" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I192" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9">
-      <c r="A193" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I193" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
-      <c r="A194" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I194" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
-      <c r="A195" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I195" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9">
-      <c r="A196" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I196" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9">
-      <c r="A197" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9">
-      <c r="A198" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I198" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9">
-      <c r="A199" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I199" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9">
-      <c r="A200" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I200" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9">
-      <c r="A201" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-      <c r="H201" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I201" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9">
-      <c r="A202" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-      <c r="H202" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I202" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9">
-      <c r="A203" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-      <c r="H203" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I203" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
-      <c r="A204" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I204" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9">
-      <c r="A205" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I205" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9">
-      <c r="A206" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-      <c r="H206" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I206" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9">
-      <c r="A207" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-      <c r="H207" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I207" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9">
-      <c r="A208" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-      <c r="H208" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I208" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9">
-      <c r="A209" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-      <c r="H209" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I209" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9">
-      <c r="A210" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I210" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9">
-      <c r="A211" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-      <c r="H211" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I211" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9">
-      <c r="A212" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-      <c r="H212" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I212" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9">
-      <c r="A213" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I213" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9">
-      <c r="A214" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I214" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9">
-      <c r="A215" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I215" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9">
-      <c r="A216" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-      <c r="H216" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I216" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9">
-      <c r="A217" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-      <c r="H217" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I217" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9">
-      <c r="A218" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-      <c r="H218" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I218" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9">
-      <c r="A219" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-      <c r="H219" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I219" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9">
-      <c r="A220" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I220" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
-      <c r="A221" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I221" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
-      <c r="A222" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I222" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9">
-      <c r="A223" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I223" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9">
-      <c r="A224" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I224" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
-      <c r="A225" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I225" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9">
-      <c r="A226" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-      <c r="H226" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I226" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9">
-      <c r="A227" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-      <c r="H227" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I227" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9">
-      <c r="A228" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-      <c r="H228" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I228" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9">
-      <c r="A229" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-      <c r="H229" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I229" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9">
-      <c r="A230" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I230" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9">
-      <c r="A231" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I231" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9">
-      <c r="A232" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-      <c r="H232" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I232" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9">
-      <c r="A233" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-      <c r="H233" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I233" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9">
-      <c r="A234" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I234" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9">
-      <c r="A235" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I235" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9">
-      <c r="A236" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-      <c r="H236" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I236" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9">
-      <c r="A237" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-      <c r="H237" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I237" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9">
-      <c r="A238" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I238" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9">
-      <c r="A239" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I239" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9">
-      <c r="A240" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-      <c r="H240" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I240" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9">
-      <c r="A241" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-      <c r="H241" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I241" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9">
-      <c r="A242" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-      <c r="H242" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I242" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9">
-      <c r="A243" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-      <c r="H243" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I243" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9">
-      <c r="A244" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I244" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9">
-      <c r="A245" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-      <c r="H245" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I245" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9">
-      <c r="A246" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-      <c r="H246" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I246" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9">
-      <c r="A247" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I247" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9">
-      <c r="A248" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I248" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9">
-      <c r="A249" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-      <c r="H249" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I249" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9">
-      <c r="A250" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-      <c r="H250" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I250" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9">
-      <c r="A251" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-      <c r="H251" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I251" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9">
-      <c r="A252" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I252" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9">
-      <c r="A253" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I253" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9">
-      <c r="A254" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-      <c r="H254" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I254" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9">
-      <c r="A255" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-      <c r="H255" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I255" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9">
-      <c r="A256" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I256" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9">
-      <c r="A257" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I257" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9">
-      <c r="A258" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I258" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9">
-      <c r="A259" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-      <c r="H259" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I259" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9">
-      <c r="A260" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-      <c r="H260" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I260" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9">
-      <c r="A261" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-      <c r="H261" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I261" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9">
-      <c r="A262" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-      <c r="H262" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I262" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9">
-      <c r="A263" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-      <c r="H263" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I263" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9">
-      <c r="A264" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I264" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9">
-      <c r="A265" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-      <c r="H265" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I265" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9">
-      <c r="A266" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-      <c r="H266" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I266" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9">
-      <c r="A267" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
-      <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-      <c r="H267" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I267" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9">
-      <c r="A268" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
-      <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-      <c r="H268" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I268" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9">
-      <c r="A269" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-      <c r="H269" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I269" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9">
-      <c r="A270" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
-      <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-      <c r="H270" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I270" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9">
-      <c r="A271" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-      <c r="H271" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I271" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9">
-      <c r="A272" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I272" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9">
-      <c r="A273" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-      <c r="H273" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I273" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9">
-      <c r="A274" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-      <c r="H274" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I274" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9">
-      <c r="A275" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-      <c r="H275" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I275" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9">
-      <c r="A276" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-      <c r="H276" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I276" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9">
-      <c r="A277" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-      <c r="H277" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I277" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9">
-      <c r="A278" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I278" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9">
-      <c r="A279" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-      <c r="H279" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I279" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9">
-      <c r="A280" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
-      <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-      <c r="H280" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I280" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9">
-      <c r="A281" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
-      <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-      <c r="H281" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I281" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9">
-      <c r="A282" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-      <c r="H282" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I282" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9">
-      <c r="A283" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D283" s="2"/>
-      <c r="E283" s="2"/>
-      <c r="F283" s="2"/>
-      <c r="G283" s="2"/>
-      <c r="H283" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I283" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9">
-      <c r="A284" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D284" s="2"/>
-      <c r="E284" s="2"/>
-      <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-      <c r="H284" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I284" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
